--- a/Databases/Database3/Output/2015/db3_2015_clean.xlsx
+++ b/Databases/Database3/Output/2015/db3_2015_clean.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R111"/>
+  <dimension ref="A1:R129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,7 +521,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>UL:S; UR:FW; LR:OB</t>
+          <t>UL:S; LL:-; UR:FW; LR:OB</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -586,14 +586,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>42046</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -623,19 +623,11 @@
           <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>H67</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>UL:S; LL:KY; UR:FY; LR:WR</t>
+          <t>UL:O; LL:G; UR:S; LR:G</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -662,14 +654,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>42046</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,7 +684,7 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -700,8 +692,16 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>UL:FG; LL:BO; UR:-; LR:WB</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>2 SNPL &amp; 6 PIPL banded</t>
@@ -726,14 +726,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>42046</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>30.06605</v>
+        <v>30.06503</v>
       </c>
       <c r="G5" t="n">
-        <v>-85.6172</v>
+        <v>-85.61772000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -767,12 +767,12 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>UL:O; LL:Lb; UR:S</t>
+          <t>UL:O; LL:O/Y; UR:S; LR:-</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1 SNPL &amp; 2 PIPL banded</t>
+          <t>2 SNPL &amp; 6 PIPL banded | Band: O/Y split band</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -794,14 +794,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>42046</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>30.06605</v>
+        <v>30.06503</v>
       </c>
       <c r="G6" t="n">
-        <v>-85.6172</v>
+        <v>-85.61772000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -832,11 +832,19 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>UL:G; LL:GY; UR:FY; LR:KK</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1 SNPL &amp; 2 PIPL banded</t>
+          <t>2 SNPL &amp; 6 PIPL banded</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -858,49 +866,61 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>42041</v>
+        <v>42046</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9:17-10:57</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sunny, cool, mild wind, low rising</t>
+          <t>Med tide, rising, 0%cloud cover, no precipitation, calm surf, 4-7 mph winds</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Buck Beach (Tyndall AFB), Bay County</t>
+          <t>Tyndall Air Force Base- Shell Island</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>29.99042</v>
+        <v>30.06503</v>
       </c>
       <c r="G7" t="n">
-        <v>-85.50476</v>
+        <v>-85.61772000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Jack Toriello, Nervalis Medina</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>H67</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>UL:S; LL:KY; UR:FY; LR:WR</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>One PIPL Banded Yf(9C8)//X:S//X</t>
+          <t>2 SNPL &amp; 6 PIPL banded</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -922,47 +942,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>42045</v>
+        <v>42046</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10:50 - 12:30</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Windy</t>
+          <t>Med tide, rising, 0%cloud cover, no precipitation, calm surf, 4-7 mph winds</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Big Marco Pass CWA</t>
+          <t>Tyndall Air Force Base- Shell Island</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>25.9512</v>
+        <v>30.06503</v>
       </c>
       <c r="G8" t="n">
-        <v>-81.75031</v>
+        <v>-85.61772000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Carol Rizkalla</t>
+          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2 SNPL &amp; 6 PIPL banded</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -982,47 +1006,55 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>42045</v>
+        <v>42046</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10:50 - 12:30</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Windy</t>
+          <t>Med tide, rising, 0%cloud cover, no precipitation, calm surf, 4-7 mph winds</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Big Marco Pass CWA</t>
+          <t>Tyndall Air Force Base- Shell Island</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>25.95483</v>
+        <v>30.06605</v>
       </c>
       <c r="G9" t="n">
-        <v>-81.75163999999999</v>
+        <v>-85.6172</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Carol Rizkalla</t>
+          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>UL:O; LL:Lb; UR:S; LR:-</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1 SNPL &amp; 2 PIPL banded</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -1042,31 +1074,31 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>42045</v>
+        <v>42046</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8:12 - 10:12</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Low 50s, windy, overcast</t>
+          <t>Med tide, rising, 0%cloud cover, no precipitation, calm surf, 4-7 mph winds</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Little Talbot Island State Park</t>
+          <t>Tyndall Air Force Base- Shell Island</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>30.4705556</v>
+        <v>30.06605</v>
       </c>
       <c r="G10" t="n">
-        <v>-81.4122222</v>
+        <v>-85.6172</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
@@ -1076,15 +1108,23 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Joan and Richard Becker</t>
+          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Lb</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>UL:S; LL:RK; UR:FLb; LR:GY</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Not banded</t>
+          <t>1 SNPL &amp; 2 PIPL banded</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1106,41 +1146,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>42045</v>
+        <v>42046</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8:12 - 10:12</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Low 50s, windy, overcast</t>
+          <t>Med tide, rising, 0%cloud cover, no precipitation, calm surf, 4-7 mph winds</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Little Talbot Island State Park</t>
+          <t>Tyndall Air Force Base- Shell Island</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>30.4327778</v>
+        <v>30.06605</v>
       </c>
       <c r="G11" t="n">
-        <v>-81.4063889</v>
+        <v>-85.6172</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Joan and Richard Becker</t>
+          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1148,7 +1188,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Not banded</t>
+          <t>1 SNPL &amp; 2 PIPL banded</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1170,41 +1210,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>42045</v>
+        <v>42041</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8:12 - 10:12</t>
+          <t>09:17 - 10:57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Low 50s, windy, overcast</t>
+          <t>Sunny, cool, mild wind, low rising</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Little Talbot Island State Park</t>
+          <t>Buck Beach (Tyndall AFB), Bay County</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30.4311111</v>
+        <v>29.99042</v>
       </c>
       <c r="G12" t="n">
-        <v>-81.4069444</v>
+        <v>-85.50476</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Joan and Richard Becker</t>
+          <t>Jack Toriello, Nervalis Medina</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1212,7 +1252,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Not banded</t>
+          <t>One PIPL Banded Yf(9C8)//X:S//X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1234,55 +1274,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>42041</v>
+        <v>42045</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9:00-11:45am</t>
+          <t>10:50 - 12:30</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>clear, sunny, wind NE 15-18mph, 52F</t>
+          <t>Windy</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Huguenot Memorial Park</t>
+          <t>Big Marco Pass CWA</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>30.420041</v>
+        <v>25.9512</v>
       </c>
       <c r="G13" t="n">
-        <v>-81.410472</v>
+        <v>-81.75031</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Shelley Beville, Joan Becker, Richard becker, Kevin Oxenrider</t>
+          <t>Carol Rizkalla</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>LR:A/B</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>PIPL WAS BANDED AND REPORTED | Band: could not see left leg. Gray band looked  beige could have faded.</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -1302,51 +1334,47 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>42046</v>
+        <v>42045</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0900-1115</t>
+          <t>10:50 - 12:30</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>mid tide rising, clear, calm, cool</t>
+          <t>Windy</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Santa Rosa Area, GUIS, North</t>
+          <t>Big Marco Pass CWA</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>30.36922</v>
+        <v>25.95483</v>
       </c>
       <c r="G14" t="n">
-        <v>-86.95502</v>
+        <v>-81.75163999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Mark Nicholas</t>
+          <t>Carol Rizkalla</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>3 banded (see data sheet #3)</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -1366,41 +1394,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>42046</v>
+        <v>42045</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0900-1115</t>
+          <t>08:12 - 10:12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>mid tide rising, clear, calm, cool</t>
+          <t>Low 50s, windy, overcast</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Santa Rosa Area, GUIS, North</t>
+          <t>Little Talbot Island State Park</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>30.3575</v>
+        <v>30.4705556</v>
       </c>
       <c r="G15" t="n">
-        <v>-87.04365</v>
+        <v>-81.4122222</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Mark Nicholas</t>
+          <t>Joan and Richard Becker</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1408,7 +1436,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>large flock of birds feeding and roosting in mud flat area; no bands observed on any of the birds</t>
+          <t>Not banded</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1430,57 +1458,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>42046</v>
+        <v>42045</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>07:30-14:30 EST</t>
+          <t>08:12 - 10:12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Clear, 47°F, winds calm</t>
+          <t>Low 50s, windy, overcast</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>St. Vincent National Wildlife Refuge</t>
+          <t>Little Talbot Island State Park</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>29.64342</v>
+        <v>30.4327778</v>
       </c>
       <c r="G16" t="n">
-        <v>-85.15213</v>
+        <v>-81.4063889</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Bradley S. Smith, Susan L. Lavender</t>
+          <t>Joan and Richard Becker</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>FO</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>UL:FO; LL:GR; UR:S; LR:K</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two banded PIPL, one with orange flag.   | Band: Foraging Gulf beaches south of Oyster Pond.  </t>
+          <t>Not banded</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1502,41 +1522,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>42046</v>
+        <v>42045</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>07:30-14:30 EST</t>
+          <t>08:12 - 10:12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Clear, 47°F, winds calm</t>
+          <t>Low 50s, windy, overcast</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St. Vincent National Wildlife Refuge</t>
+          <t>Little Talbot Island State Park</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>29.64342</v>
+        <v>30.4311111</v>
       </c>
       <c r="G17" t="n">
-        <v>-85.15213</v>
+        <v>-81.4069444</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Bradley S. Smith, Susan L. Lavender</t>
+          <t>Joan and Richard Becker</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1544,7 +1564,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two banded PIPL, one with orange flag.  </t>
+          <t>Not banded</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1566,49 +1586,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>42042</v>
+        <v>42041</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>09:00 - 11:45</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Low tide rising, 40% cloud cover, no precipitation, surf calm, 4-7 mph winds</t>
+          <t>clear, sunny, wind NE 15-18mph, 52F</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Alligator Point- Phipps Preserve</t>
+          <t>Huguenot Memorial Park</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>29.90897</v>
+        <v>30.420041</v>
       </c>
       <c r="G18" t="n">
-        <v>-84.43456999999999</v>
+        <v>-81.410472</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Marvin Friel, Raya Pruner, Kevin Christman, Ezra Thompson, Caity Reiland-Smith</t>
+          <t>Shelley Beville, Joan Becker, Richard becker, Kevin Oxenrider</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:A/B</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1 PIPL banded</t>
+          <t>PIPL WAS BANDED AND REPORTED | Band: could not see left leg. Gray band looked  beige could have faded.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1630,57 +1654,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>42042</v>
+        <v>42046</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>09:00 - 11:15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Low tide rising, 40% cloud cover, no precipitation, surf calm, 4-7 mph winds</t>
+          <t>mid tide rising, clear, calm, cool</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Alligator Point- Phipps Preserve</t>
+          <t>Santa Rosa Area, GUIS, North</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>29.91434</v>
+        <v>30.36922</v>
       </c>
       <c r="G19" t="n">
-        <v>-84.44094</v>
+        <v>-86.95502</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Marvin Friel, Raya Pruner, Kevin Christman, Ezra Thompson, Caity Reiland-Smith</t>
+          <t>Mark Nicholas</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>UL:FG; LL:BB; LR:Y</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2 PIPL banded | Band: photos taken</t>
+          <t>3 banded (see data sheet #3)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1702,61 +1718,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>42042</v>
+        <v>42046</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>09:00 - 11:15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Low tide rising, 40% cloud cover, no precipitation, surf calm, 4-7 mph winds</t>
+          <t>mid tide rising, clear, calm, cool</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Alligator Point- Phipps Preserve</t>
+          <t>Santa Rosa Area, GUIS, North</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>29.91434</v>
+        <v>30.3575</v>
       </c>
       <c r="G20" t="n">
-        <v>-84.44094</v>
+        <v>-87.04365</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Marvin Friel, Raya Pruner, Kevin Christman, Ezra Thompson, Caity Reiland-Smith</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>T14</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>UL:S; LL:OB; UR:FY; LR:GY</t>
-        </is>
-      </c>
+          <t>Mark Nicholas</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2 PIPL banded | Band: photos taken</t>
+          <t>large flock of birds feeding and roosting in mud flat area; no bands observed on any of the birds</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1778,49 +1782,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>42042</v>
+        <v>42046</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>07:30 - 14:30</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Low tide rising, 40% cloud cover, no precipitation, surf calm, 4-7 mph winds</t>
+          <t>Clear, 47°F, winds calm</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Alligator Point- Phipps Preserve</t>
+          <t>St. Vincent National Wildlife Refuge</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>29.91434</v>
+        <v>29.64342</v>
       </c>
       <c r="G21" t="n">
-        <v>-84.44094</v>
+        <v>-85.15213</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Marvin Friel, Raya Pruner, Kevin Christman, Ezra Thompson, Caity Reiland-Smith</t>
+          <t>Bradley S. Smith, Susan L. Lavender</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>FO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>UL:FO; LL:GR; UR:S; LR:K</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2 PIPL banded</t>
+          <t xml:space="preserve">Two banded PIPL, one with orange flag.   | Band: Foraging Gulf beaches south of Oyster Pond.  </t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1842,53 +1854,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>42047</v>
+        <v>42046</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>07:30 - 14:30</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Med tide, rising, 0% cloud cover, no precipitation, calm surf, 8-12 mph winds</t>
+          <t>Clear, 47°F, winds calm</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>St. George Island State Park</t>
+          <t>St. Vincent National Wildlife Refuge</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>29.74834</v>
+        <v>29.64342</v>
       </c>
       <c r="G22" t="n">
-        <v>-84.71011</v>
+        <v>-85.15213</v>
       </c>
       <c r="H22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Marvin Friel</t>
+          <t>Bradley S. Smith, Susan L. Lavender</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>UL:S; LL:Y/O; UR:O; LR:Y</t>
+          <t>UL:-; LL:G; UR:FG; LR:GK</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Band: Y/O SPLIT BAND</t>
+          <t xml:space="preserve">Two banded PIPL, one with orange flag.   | Band: Foraging Gulf beaches south of Oyster Pond.  </t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1910,59 +1926,51 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>42047</v>
+        <v>42046</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>07:30 - 14:30</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Med tide, rising, 0% cloud cover, no precipitation, calm surf, 8-12 mph winds</t>
+          <t>Clear, 47°F, winds calm</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St. George Island State Park</t>
+          <t>St. Vincent National Wildlife Refuge</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>29.74834</v>
+        <v>29.64342</v>
       </c>
       <c r="G23" t="n">
-        <v>-84.71011</v>
+        <v>-85.15213</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Marvin Friel</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>P72</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>UL:FY; UR:S</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>Bradley S. Smith, Susan L. Lavender</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two banded PIPL, one with orange flag.  </t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -1982,57 +1990,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>42046</v>
+        <v>42042</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Low tide, Sunny, 0% cloud cover, 15 knot winds, moderate seas</t>
+          <t>Low tide rising, 40% cloud cover, no precipitation, surf calm, 4-7 mph winds</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dog Island</t>
+          <t>Alligator Point- Phipps Preserve</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>29.7817</v>
+        <v>29.90897</v>
       </c>
       <c r="G24" t="n">
-        <v>-84.65154</v>
+        <v>-84.43456999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Steve Mullin,     Kevin Christman</t>
+          <t>Marvin Friel, Raya Pruner, Kevin Christman, Ezra Thompson, Caity Reiland-Smith</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>UL:S; LL:GTeal; UR:Yf; LR:YK</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2 banded SNPL, 2 banded PIPL | Band: Either teal or light blue</t>
+          <t>1 PIPL banded</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2054,49 +2054,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>42046</v>
+        <v>42042</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Low tide, Sunny, 0% cloud cover, 15 knot winds, moderate seas</t>
+          <t>Low tide rising, 40% cloud cover, no precipitation, surf calm, 4-7 mph winds</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dog Island</t>
+          <t>Alligator Point- Phipps Preserve</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>29.7817</v>
+        <v>29.91434</v>
       </c>
       <c r="G25" t="n">
-        <v>-84.65154</v>
+        <v>-84.44094</v>
       </c>
       <c r="H25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Steve Mullin,     Kevin Christman</t>
+          <t>Marvin Friel, Raya Pruner, Kevin Christman, Ezra Thompson, Caity Reiland-Smith</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>UL:FG; LL:BB; UR:-; LR:Y</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2 banded SNPL, 2 banded PIPL</t>
+          <t>2 PIPL banded | Band: photos taken</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2118,49 +2126,61 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>42046</v>
+        <v>42042</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Low tide, Sunny, 0% cloud cover, 15 knot winds, moderate seas</t>
+          <t>Low tide rising, 40% cloud cover, no precipitation, surf calm, 4-7 mph winds</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dog Island</t>
+          <t>Alligator Point- Phipps Preserve</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>29.78925</v>
+        <v>29.91434</v>
       </c>
       <c r="G26" t="n">
-        <v>-84.64162</v>
+        <v>-84.44094</v>
       </c>
       <c r="H26" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Steve Mullin,     Kevin Christman</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+          <t>Marvin Friel, Raya Pruner, Kevin Christman, Ezra Thompson, Caity Reiland-Smith</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>UL:S; LL:OB; UR:FY; LR:GY</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Not Banded</t>
+          <t>2 PIPL banded | Band: photos taken</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2182,57 +2202,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>42047</v>
+        <v>42042</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1130-1230</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Medium tide rising, Mostly sunny 10% cloud cover, 10knots wind, moderate seas gulfside</t>
+          <t>Low tide rising, 40% cloud cover, no precipitation, surf calm, 4-7 mph winds</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Flag Island NW</t>
+          <t>Alligator Point- Phipps Preserve</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>29.64164</v>
+        <v>29.91434</v>
       </c>
       <c r="G27" t="n">
-        <v>-85.15533000000001</v>
+        <v>-84.44094</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Steve Mullin</t>
+          <t>Marvin Friel, Raya Pruner, Kevin Christman, Ezra Thompson, Caity Reiland-Smith</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>UL:X; LL:GG; UR:Gf; LR:GK</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1 PIPL banded</t>
+          <t>2 PIPL banded</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2254,47 +2266,55 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>42047</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>12:34-2;45</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>clear, wind SE 10k</t>
+          <t>Med tide, rising, 0% cloud cover, no precipitation, calm surf, 8-12 mph winds</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yent bayou/ Royal Bluff</t>
+          <t>St. George Island State Park</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>29.47143</v>
+        <v>29.74834</v>
       </c>
       <c r="G28" t="n">
-        <v>-84.46089000000001</v>
+        <v>-84.71011</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Susan Cerulean, Mike Miller</t>
+          <t>Marvin Friel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>UL:S; LL:Y/O; UR:O; LR:Y</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Band: Y/O SPLIT BAND</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -2314,48 +2334,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>42046</v>
+        <v>42047</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11:00-3:30</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>clear,winds SE 10k to SW 10k</t>
+          <t>Med tide, rising, 0% cloud cover, no precipitation, calm surf, 8-12 mph winds</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lanack Reef</t>
+          <t>St. George Island State Park</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>29.52505</v>
+        <v>29.74834</v>
       </c>
       <c r="G29" t="n">
-        <v>-84.34397</v>
+        <v>-84.71011</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Susan Cerulean, Mike Miller</t>
+          <t>Marvin Friel</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>UL:Y; LL:B; UR:S; LR:W</t>
+          <t>UL:-; LL:YO; UR:FG; LR:WY</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2378,46 +2402,58 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>42046</v>
+        <v>42047</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>11:00-3:30</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>clear,winds SE 10k to SW 10k</t>
+          <t>Med tide, rising, 0% cloud cover, no precipitation, calm surf, 8-12 mph winds</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lanack Reef</t>
+          <t>St. George Island State Park</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>29.52505</v>
+        <v>29.74834</v>
       </c>
       <c r="G30" t="n">
-        <v>-84.34397</v>
+        <v>-84.71011</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Susan Cerulean, Mike Miller</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+          <t>Marvin Friel</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>P72</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>UL:FY; LL:-; UR:S; LR:-</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
@@ -2438,46 +2474,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>42046</v>
+        <v>42047</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11:00-3:30</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>clear,winds SE 10k to SW 10k</t>
+          <t>Med tide, rising, 0% cloud cover, no precipitation, calm surf, 8-12 mph winds</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lanack Reef</t>
+          <t>St. George Island State Park</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>29.52325</v>
+        <v>29.74834</v>
       </c>
       <c r="G31" t="n">
-        <v>-84.35212</v>
+        <v>-84.71011</v>
       </c>
       <c r="H31" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Susan Cerulean, Mike Miller</t>
+          <t>Marvin Friel</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>UL:FK; LL:R; UR:S; LR:YO</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
@@ -2498,55 +2542,47 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>42041</v>
+        <v>42047</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Med tide, rising, 10% cloud cover, no precipitation, moderate surf, 8-12 mph winds</t>
+          <t>Med tide, rising, 0% cloud cover, no precipitation, calm surf, 8-12 mph winds</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>St. Joseph Peninsula State Park</t>
+          <t>St. George Island State Park</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>29.82907</v>
+        <v>29.74834</v>
       </c>
       <c r="G32" t="n">
-        <v>-85.41045</v>
+        <v>-84.71011</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
+          <t>Marvin Friel</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>UL:O; UR:S; LR:Lg/O/Lg</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>1 banded | Band: lower right, triple stripe band</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -2566,57 +2602,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>42041</v>
+        <v>42046</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Med tide, rising, 10% cloud cover, no precipitation, moderate surf, 8-12 mph winds</t>
+          <t>Low tide, Sunny, 0% cloud cover, 15 knot winds, moderate seas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>St. Joseph Peninsula State Park</t>
+          <t>Dog Island</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>29.84514</v>
+        <v>29.7817</v>
       </c>
       <c r="G33" t="n">
-        <v>-85.40340999999999</v>
+        <v>-84.65154</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
+          <t>Steve Mullin,     Kevin Christman</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>UL:FG; LL:BK; LR:GY</t>
+          <t>UL:S; LL:GTeal; UR:Yf; LR:YK</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2 PIPL banded</t>
+          <t>2 banded SNPL, 2 banded PIPL | Band: Either teal or light blue</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2638,49 +2674,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>42041</v>
+        <v>42046</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Med tide, rising, 10% cloud cover, no precipitation, moderate surf, 8-12 mph winds</t>
+          <t>Low tide, Sunny, 0% cloud cover, 15 knot winds, moderate seas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>St. Joseph Peninsula State Park</t>
+          <t>Dog Island</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>29.84514</v>
+        <v>29.7817</v>
       </c>
       <c r="G34" t="n">
-        <v>-85.40340999999999</v>
+        <v>-84.65154</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
+          <t>Steve Mullin,     Kevin Christman</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>UL:Of; LL:Ob; UR:S; LR:X</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2 PIPL banded</t>
+          <t>2 banded SNPL, 2 banded PIPL</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2702,57 +2746,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>42041</v>
+        <v>42046</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Med tide, rising, 10% cloud cover, no precipitation, moderate surf, 8-12 mph winds</t>
+          <t>Low tide, Sunny, 0% cloud cover, 15 knot winds, moderate seas</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>St. Joseph Peninsula State Park</t>
+          <t>Dog Island</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>29.8437</v>
+        <v>29.7817</v>
       </c>
       <c r="G35" t="n">
-        <v>-85.41562999999999</v>
+        <v>-84.65154</v>
       </c>
       <c r="H35" t="n">
+        <v>11</v>
+      </c>
+      <c r="I35" t="n">
         <v>5</v>
       </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
+          <t>Steve Mullin,     Kevin Christman</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>UL:FG; LL:YB; LR:WR</t>
-        </is>
-      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1 PIPL &amp; 4 SNPL banded</t>
+          <t>2 banded SNPL, 2 banded PIPL</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2774,61 +2810,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>42045</v>
+        <v>42046</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
+          <t>Low tide, Sunny, 0% cloud cover, 15 knot winds, moderate seas</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Indian Pass</t>
+          <t>Dog Island</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>29.68289</v>
+        <v>29.78925</v>
       </c>
       <c r="G36" t="n">
-        <v>-85.30714</v>
+        <v>-84.64162</v>
       </c>
       <c r="H36" t="n">
+        <v>13</v>
+      </c>
+      <c r="I36" t="n">
         <v>4</v>
       </c>
-      <c r="I36" t="n">
-        <v>1</v>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Jack Toriello</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Black Dot</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>UL:O; LL:b; UR:S; LR:(O/b)</t>
-        </is>
-      </c>
+          <t>Steve Mullin,     Kevin Christman</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>PIPL banded | Band: Black dot on Upper Left O, Lower Right (O/b) is split band</t>
+          <t>Not Banded</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2850,61 +2874,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>42045</v>
+        <v>42047</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>11:30 - 12:30</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
+          <t>Medium tide rising, Mostly sunny 10% cloud cover, 10knots wind, moderate seas gulfside</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Indian Pass</t>
+          <t>Flag Island NW</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>29.68211</v>
+        <v>29.64164</v>
       </c>
       <c r="G37" t="n">
-        <v>-85.31211</v>
+        <v>-85.15533000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Jack Toriello</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>V45</t>
-        </is>
-      </c>
+          <t>Steve Mullin</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:S; LL:GY; UR:Yf; LR:WY</t>
+          <t>UL:X; LL:GG; UR:Gf; LR:GK</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>PIPL banded</t>
+          <t>1 PIPL banded</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2926,61 +2946,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>42045</v>
+        <v>42047</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>11:30 - 12:30</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
+          <t>Medium tide rising, Mostly sunny 10% cloud cover, 10knots wind, moderate seas gulfside</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Indian Pass</t>
+          <t>Flag Island NW</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>29.68034</v>
+        <v>29.64164</v>
       </c>
       <c r="G38" t="n">
-        <v>-85.31994</v>
+        <v>-85.15533000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Jack Toriello</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>2C9</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Orientation:Horizontal; UL:Yf; UR:S</t>
-        </is>
-      </c>
+          <t>Steve Mullin</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>4 PIPL banded</t>
+          <t>1 PIPL banded</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3002,59 +3010,47 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>42045</v>
+        <v>42047</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>12:34 - 02:45</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
+          <t>clear, wind SE 10k</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Indian Pass</t>
+          <t>Yent bayou/ Royal Bluff</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>29.68034</v>
+        <v>29.47143</v>
       </c>
       <c r="G39" t="n">
-        <v>-85.31994</v>
+        <v>-84.46089000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Jack Toriello</t>
+          <t>Susan Cerulean, Mike Miller</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>UL:Gf; LL:OO; LR:WB</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>4 PIPL banded | Band: no service band</t>
-        </is>
-      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -3074,63 +3070,51 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>42045</v>
+        <v>42046</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>11:00 - 03:30</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
+          <t>clear,winds SE 10k to SW 10k</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Indian Pass</t>
+          <t>Lanack Reef</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>29.68034</v>
+        <v>29.52505</v>
       </c>
       <c r="G40" t="n">
-        <v>-85.31994</v>
+        <v>-84.34397</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Jack Toriello</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
+          <t>Susan Cerulean, Mike Miller</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:Yf; LL:RR; UR:S; LR:YK</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>4 PIPL banded | Band: RR badly faded</t>
-        </is>
-      </c>
+          <t>UL:Y; LL:B; UR:S; LR:W</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -3150,51 +3134,47 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>42045</v>
+        <v>42046</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>11:00 - 03:30</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
+          <t>clear,winds SE 10k to SW 10k</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Indian Pass</t>
+          <t>Lanack Reef</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>29.68034</v>
+        <v>29.52505</v>
       </c>
       <c r="G41" t="n">
-        <v>-85.31994</v>
+        <v>-84.34397</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Jack Toriello</t>
+          <t>Susan Cerulean, Mike Miller</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>4 PIPL banded</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -3214,51 +3194,47 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>42045</v>
+        <v>42046</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>11:00 - 03:30</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
+          <t>clear,winds SE 10k to SW 10k</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Indian Pass</t>
+          <t>Lanack Reef</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>29.67749</v>
+        <v>29.52325</v>
       </c>
       <c r="G42" t="n">
-        <v>-85.32943</v>
+        <v>-84.35212</v>
       </c>
       <c r="H42" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Jack Toriello</t>
+          <t>Susan Cerulean, Mike Miller</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>PIPL Unbanded</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -3278,31 +3254,31 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>42046</v>
+        <v>42041</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sunny, Calm winds, Low tide rising, chilly</t>
+          <t>Med tide, rising, 10% cloud cover, no precipitation, moderate surf, 8-12 mph winds</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St. Joes Bay- South</t>
+          <t>St. Joseph Peninsula State Park</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>29.69362</v>
+        <v>29.82907</v>
       </c>
       <c r="G43" t="n">
-        <v>-85.31256999999999</v>
+        <v>-85.41045</v>
       </c>
       <c r="H43" t="n">
         <v>2</v>
@@ -3312,27 +3288,19 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Jack Toriello</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Black Dot</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
+          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>UL:O; LL:b; UR:S; LR:(O/b)</t>
+          <t>UL:O; LL:-; UR:S; LR:Lg/O/Lg</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1 WIPL Banded, 3PIPL Banded | Band: Black dot on Upper Left O, Lower Right (O/b) is split band</t>
+          <t>1 banded | Band: lower right, triple stripe band</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3354,61 +3322,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>42046</v>
+        <v>42041</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sunny, Calm winds, Low tide rising, chilly</t>
+          <t>Med tide, rising, 10% cloud cover, no precipitation, moderate surf, 8-12 mph winds</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>St. Joes Bay- South</t>
+          <t>St. Joseph Peninsula State Park</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>29.69362</v>
+        <v>29.84514</v>
       </c>
       <c r="G44" t="n">
-        <v>-85.31256999999999</v>
+        <v>-85.40340999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Jack Toriello</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>V45</t>
-        </is>
-      </c>
+          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>G</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:S; LL:GY; UR:Yf; LR:WY</t>
+          <t>UL:FG; LL:BK; UR:-; LR:GY</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1 WIPL Banded, 3PIPL Banded</t>
+          <t>2 PIPL banded</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3430,61 +3394,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>42046</v>
+        <v>42041</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sunny, Calm winds, Low tide rising, chilly</t>
+          <t>Med tide, rising, 10% cloud cover, no precipitation, moderate surf, 8-12 mph winds</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St. Joes Bay- South</t>
+          <t>St. Joseph Peninsula State Park</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>29.69362</v>
+        <v>29.84514</v>
       </c>
       <c r="G45" t="n">
-        <v>-85.31256999999999</v>
+        <v>-85.40340999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Jack Toriello</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
+          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>G</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:Yf; LL:RR; UR:S; LR:YK</t>
+          <t>UL:G; LL:KK; UR:FG; LR:-</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1 WIPL Banded, 3PIPL Banded | Band: RR badly faded</t>
+          <t>2 PIPL banded</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3506,41 +3466,41 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>42046</v>
+        <v>42041</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sunny, Calm winds, Low tide rising, chilly</t>
+          <t>Med tide, rising, 10% cloud cover, no precipitation, moderate surf, 8-12 mph winds</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>St. Joes Bay- South</t>
+          <t>St. Joseph Peninsula State Park</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>29.69362</v>
+        <v>29.84514</v>
       </c>
       <c r="G46" t="n">
-        <v>-85.31256999999999</v>
+        <v>-85.40340999999999</v>
       </c>
       <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="n">
         <v>2</v>
       </c>
-      <c r="I46" t="n">
-        <v>1</v>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Jack Toriello</t>
+          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3548,7 +3508,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1 WIPL Banded, 3PIPL Banded</t>
+          <t>2 PIPL banded</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3570,53 +3530,57 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>42043</v>
+        <v>42041</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>8:20-10:20 am</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sunny, wind E 7 mph, 65 degrees</t>
+          <t>Med tide, rising, 10% cloud cover, no precipitation, moderate surf, 8-12 mph winds</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cayo Costa R3</t>
+          <t>St. Joseph Peninsula State Park</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>26.66909</v>
+        <v>29.8437</v>
       </c>
       <c r="G47" t="n">
-        <v>-82.25515</v>
+        <v>-85.41562999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Marie Di Rosa</t>
+          <t>Marvin Friel, Ezra Thompson, Caity Reiland-Smith</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>UL:R; LL:G/B; LR:Y/G/R</t>
+          <t>UL:FG; LL:YB; UR:-; LR:WR</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1 PIPL banded, data entered by Charlie Ewell</t>
+          <t>1 PIPL &amp; 4 SNPL banded</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3638,49 +3602,61 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>42043</v>
+        <v>42045</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>8:20-10:20 am</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sunny, wind E 7 mph, 65 degrees</t>
+          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cayo Costa R3</t>
+          <t>Indian Pass</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>26.66909</v>
+        <v>29.68289</v>
       </c>
       <c r="G48" t="n">
-        <v>-82.25515</v>
+        <v>-85.30714</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Marie Di Rosa</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+          <t>Jack Toriello</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Black Dot</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>UL:O; LL:b; UR:S; LR:(O/b)</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1 PIPL banded, data entered by Charlie Ewell</t>
+          <t>PIPL banded | Band: Black dot on Upper Left O, Lower Right (O/b) is split band</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3702,49 +3678,61 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>42041</v>
+        <v>42045</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9:40 am - 12:10 pm</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sunny, wind NNE 17 mph, 65-70 degrees</t>
+          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ft Myers Beach R1</t>
+          <t>Indian Pass</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>26.46573</v>
+        <v>29.68211</v>
       </c>
       <c r="G49" t="n">
-        <v>-81.96758</v>
+        <v>-85.31211</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I49" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Marie Di Rosa</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+          <t>Jack Toriello</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>V45</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Orientation:Horizontal; UL:S; LL:GY; UR:Yf; LR:WY</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Plovers roosting near rock groin.  Other species along intertidal zone.  Data entered by Charlie Ewell</t>
+          <t>PIPL banded</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3766,49 +3754,61 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>42042</v>
+        <v>42045</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>7:30 - 9:00 am</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sunny, wind calm, 60 degrees</t>
+          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bunche Beach</t>
+          <t>Indian Pass</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>26.477372</v>
+        <v>29.68034</v>
       </c>
       <c r="G50" t="n">
-        <v>-81.970591</v>
+        <v>-85.31994</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I50" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Charlie Ewell, Walt Winton</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+          <t>Jack Toriello</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2C9</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Orientation:Horizontal; UL:Yf; LL:-; UR:S; LR:-</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Foraging groups on incoming tide.  Data entered by Charlie Ewell</t>
+          <t>4 PIPL banded</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3830,49 +3830,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>42042</v>
+        <v>42045</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1245-1430</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Clear, W-S 10, 50s</t>
+          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cedar Key West </t>
+          <t>Indian Pass</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>29.155982</v>
+        <v>29.68034</v>
       </c>
       <c r="G51" t="n">
-        <v>-83.06677000000001</v>
+        <v>-85.31994</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Doris and Pat Leary</t>
+          <t>Jack Toriello</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>UL:Gf; LL:OO; UR:-; LR:WB</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2 banded PIPL FY[A59] and FY[J74]</t>
+          <t>4 PIPL banded | Band: no service band</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3894,49 +3902,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>42042</v>
+        <v>42045</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1245-1430</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Clear, W-S 10, 50s</t>
+          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cedar Key West </t>
+          <t>Indian Pass</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>29.143642</v>
+        <v>29.68034</v>
       </c>
       <c r="G52" t="n">
-        <v>-83.06456300000001</v>
+        <v>-85.31994</v>
       </c>
       <c r="H52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Doris and Pat Leary</t>
+          <t>Jack Toriello</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>UL:Of; LL:RR; UR:-; LR:bS</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>flock of BBPL and REKN (100) passed over site toward distant roost to west in gulf</t>
+          <t>4 PIPL banded</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3958,47 +3974,63 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B53" s="1" t="n">
         <v>42045</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>12:20 - 16:07</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>64F, wind NW 18-25mph</t>
+          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Longboat Key-North</t>
+          <t>Indian Pass</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>27.42262</v>
+        <v>29.68034</v>
       </c>
       <c r="G53" t="n">
-        <v>-82.67205</v>
+        <v>-85.31994</v>
       </c>
       <c r="H53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Steven Sauers</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>Jack Toriello</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Orientation:Horizontal; UL:Yf; LL:RR; UR:S; LR:YK</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>4 PIPL banded | Band: RR badly faded</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -4018,55 +4050,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>42044</v>
+        <v>42045</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>light rain first 90 min; cloudy; &lt;5</t>
+          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Crandon Park Beach, Key Biscayne</t>
+          <t>Indian Pass</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>25.701205</v>
+        <v>29.68034</v>
       </c>
       <c r="G54" t="n">
-        <v>-80.154668</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
+        <v>-85.31994</v>
+      </c>
+      <c r="H54" t="n">
+        <v>6</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Robin Diaz, Miriam Avello</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Of,OB:X,b</t>
-        </is>
-      </c>
+          <t>Jack Toriello</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
+          <t>4 PIPL banded</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4088,55 +4114,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>42044</v>
+        <v>42045</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>light rain first 90 min; cloudy; &lt;5</t>
+          <t>Sunny, Chilly, Moderate wind, Mid tide</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Crandon Park Beach, Key Biscayne</t>
+          <t>Indian Pass</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>25.701205</v>
+        <v>29.67749</v>
       </c>
       <c r="G55" t="n">
-        <v>-80.154668</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
+        <v>-85.32943</v>
+      </c>
+      <c r="H55" t="n">
+        <v>7</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Robin Diaz, Miriam Avello</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>ANF,-:X,- (N75)</t>
-        </is>
-      </c>
+          <t>Jack Toriello</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
+          <t>PIPL Unbanded</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4158,55 +4178,61 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>42044</v>
+        <v>42046</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>light rain first 90 min; cloudy; &lt;5</t>
+          <t>Sunny, Calm winds, Low tide rising, chilly</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crandon Park Beach, Key Biscayne</t>
+          <t>St. Joes Bay- South</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>25.701205</v>
+        <v>29.69362</v>
       </c>
       <c r="G56" t="n">
-        <v>-80.154668</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
+        <v>-85.31256999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Robin Diaz, Miriam Avello</t>
+          <t>Jack Toriello</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X,O/Y:O,Y</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+          <t>Black Dot</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>UL:O; LL:b; UR:S; LR:(O/b)</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
+          <t>1 WIPL Banded, 3PIPL Banded | Band: Black dot on Upper Left O, Lower Right (O/b) is split band</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4228,51 +4254,61 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>42044</v>
+        <v>42046</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>light rain first 90 min; cloudy; &lt;5</t>
+          <t>Sunny, Calm winds, Low tide rising, chilly</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crandon Park Beach, Key Biscayne</t>
+          <t>St. Joes Bay- South</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>25.701205</v>
+        <v>29.69362</v>
       </c>
       <c r="G57" t="n">
-        <v>-80.154668</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
+        <v>-85.31256999999999</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Robin Diaz, Miriam Avello</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+          <t>Jack Toriello</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>V45</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Orientation:Horizontal; UL:S; LL:GY; UR:Yf; LR:WY</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>3 PIPL banded (see Data Sheet 3)</t>
+          <t>1 WIPL Banded, 3PIPL Banded</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4294,55 +4330,61 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>42044</v>
+        <v>42046</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>light rain first 90 min; cloudy; &lt;5</t>
+          <t>Sunny, Calm winds, Low tide rising, chilly</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Crandon Park Beach, Key Biscayne</t>
+          <t>St. Joes Bay- South</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>25.700689</v>
+        <v>29.69362</v>
       </c>
       <c r="G58" t="n">
-        <v>-80.154995</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
+        <v>-85.31256999999999</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2</v>
       </c>
       <c r="I58" t="n">
         <v>1</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Robin Diaz, Miriam Avello</t>
+          <t>Jack Toriello</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>X,YG:bf,GK</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Orientation:Horizontal; UL:Yf; LL:RR; UR:S; LR:YK</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2 PIPL banded (see Data Sheet 3) | Band: photo available</t>
+          <t>1 WIPL Banded, 3PIPL Banded | Band: RR badly faded</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4364,55 +4406,49 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>42044</v>
+        <v>42046</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>light rain first 90 min; cloudy; &lt;5</t>
+          <t>Sunny, Calm winds, Low tide rising, chilly</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crandon Park Beach, Key Biscayne</t>
+          <t>St. Joes Bay- South</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>25.700689</v>
+        <v>29.69362</v>
       </c>
       <c r="G59" t="n">
-        <v>-80.154995</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
+        <v>-85.31256999999999</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Robin Diaz, Miriam Avello</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>O(green dot),-:X,Y</t>
-        </is>
-      </c>
+          <t>Jack Toriello</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2 PIPL banded (see Data Sheet 3) | Band: photo available</t>
+          <t>1 WIPL Banded, 3PIPL Banded</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4434,51 +4470,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>42044</v>
+        <v>42043</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>08:20 - 10:20</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>light rain first 90 min; cloudy; &lt;5</t>
+          <t>Sunny, wind E 7 mph, 65 degrees</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crandon Park Beach, Key Biscayne</t>
+          <t>Cayo Costa R3</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>25.700689</v>
+        <v>26.66909</v>
       </c>
       <c r="G60" t="n">
-        <v>-80.154995</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
+        <v>-82.25515</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Robin Diaz, Miriam Avello</t>
+          <t>Marie Di Rosa</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>UL:R; LL:G/B; UR:-; LR:Y/G/R</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2 PIPL banded (see Data Sheet 3)</t>
+          <t>1 PIPL banded, data entered by Charlie Ewell</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4500,55 +4538,49 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>42044</v>
+        <v>42043</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>08:20 - 10:20</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>light rain first 90 min; cloudy; &lt;5</t>
+          <t>Sunny, wind E 7 mph, 65 degrees</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Crandon Park Beach, Key Biscayne</t>
+          <t>Cayo Costa R3</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>25.70208</v>
+        <v>26.66909</v>
       </c>
       <c r="G61" t="n">
-        <v>-80.15433400000001</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
+        <v>-82.25515</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Robin Diaz, Miriam Avello</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>ANF(CC2),-:O(840),-</t>
-        </is>
-      </c>
+          <t>Marie Di Rosa</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
+          <t>1 PIPL banded, data entered by Charlie Ewell</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4570,55 +4602,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>42044</v>
+        <v>42041</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>09:40 - 12:10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>light rain first 90 min; cloudy; &lt;5</t>
+          <t>Sunny, wind NNE 17 mph, 65-70 degrees</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Crandon Park Beach, Key Biscayne</t>
+          <t>Ft Myers Beach R1</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>25.70208</v>
+        <v>26.46573</v>
       </c>
       <c r="G62" t="n">
-        <v>-80.15433400000001</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
+        <v>-81.96758</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Robin Diaz, Miriam Avello</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>X,bR:ANF,YG (T74)</t>
-        </is>
-      </c>
+          <t>Marie Di Rosa</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
+          <t>Plovers roosting near rock groin.  Other species along intertidal zone.  Data entered by Charlie Ewell</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4640,55 +4666,49 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>42044</v>
+        <v>42042</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>07:30 - 09:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>light rain first 90 min; cloudy; &lt;5</t>
+          <t>Sunny, wind calm, 60 degrees</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Crandon Park Beach, Key Biscayne</t>
+          <t>Bunche Beach</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>25.70208</v>
+        <v>26.477372</v>
       </c>
       <c r="G63" t="n">
-        <v>-80.15433400000001</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
+        <v>-81.970591</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Robin Diaz, Miriam Avello</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Of,GG:X,Y</t>
-        </is>
-      </c>
+          <t>Charlie Ewell, Walt Winton</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
+          <t>Foraging groups on incoming tide.  Data entered by Charlie Ewell</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4710,55 +4730,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>42044</v>
+        <v>42042</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>12:45 - 14:30</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>light rain first 90 min; cloudy; &lt;5</t>
+          <t>Clear, W-S 10, 50s</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Crandon Park Beach, Key Biscayne</t>
+          <t xml:space="preserve">Cedar Key West </t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>25.70208</v>
+        <v>29.155982</v>
       </c>
       <c r="G64" t="n">
-        <v>-80.15433400000001</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
+        <v>-83.06677000000001</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Robin Diaz, Miriam Avello</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Of,OR:X,Y</t>
-        </is>
-      </c>
+          <t>Doris and Pat Leary</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
+          <t>2 banded PIPL FY[A59] and FY[J74]</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4780,43 +4794,41 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>42044</v>
+        <v>42042</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>12:45 - 14:30</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>light rain first 90 min; cloudy; &lt;5</t>
+          <t>Clear, W-S 10, 50s</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Crandon Park Beach, Key Biscayne</t>
+          <t xml:space="preserve">Cedar Key West </t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>25.70208</v>
+        <v>29.143642</v>
       </c>
       <c r="G65" t="n">
-        <v>-80.15433400000001</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
+        <v>-83.06456300000001</v>
+      </c>
+      <c r="H65" t="n">
+        <v>4</v>
       </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Robin Diaz, Miriam Avello</t>
+          <t>Doris and Pat Leary</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4824,7 +4836,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>4 PIPL banded (see Data Sheet 3)</t>
+          <t>flock of BBPL and REKN (100) passed over site toward distant roost to west in gulf</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -4846,59 +4858,47 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>42046</v>
+        <v>42045</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>8:45-10:45</t>
+          <t>12:20 - 16:07</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>63 F, 9.7 E. winds, partly cloudy</t>
+          <t>64F, wind NW 18-25mph</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Boca Grande Key</t>
+          <t>Longboat Key-North</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>24.53105</v>
+        <v>27.42262</v>
       </c>
       <c r="G66" t="n">
-        <v>-82.00763999999999</v>
+        <v>-82.67205</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Patty Kelly, Sid Maddock, F. Bell</t>
+          <t>Steven Sauers</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Flg Lb</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>UL:FWS; LL:Y/R; UR:Flg Lb; LR:K/K</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>foraging nearby mixed flock on interior mud and algal flats.</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -4918,49 +4918,59 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>42046</v>
+        <v>42044</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>8:45-10:45</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>63 F, 9.7 E. winds, partly cloudy</t>
+          <t>light rain first 90 min; cloudy; &lt;5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Boca Grande Key</t>
+          <t>Crandon Park Beach, Key Biscayne</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>24.53105</v>
+        <v>25.701205</v>
       </c>
       <c r="G67" t="n">
-        <v>-82.00763999999999</v>
-      </c>
-      <c r="H67" t="n">
-        <v>1</v>
+        <v>-80.154668</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Patty Kelly, Sid Maddock, F. Bell</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>Robin Diaz, Miriam Avello</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Of,OB:X,b</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>foraging nearby mixed flock on interior mud and algal flats.</t>
+          <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -4982,61 +4992,59 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>clear, 48F, Nwind @ 20kn</t>
+          <t>light rain first 90 min; cloudy; &lt;5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>North Anclote Bar</t>
+          <t>Crandon Park Beach, Key Biscayne</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>28.23463</v>
+        <v>25.701205</v>
       </c>
       <c r="G68" t="n">
-        <v>-82.8372</v>
-      </c>
-      <c r="H68" t="n">
-        <v>2</v>
+        <v>-80.154668</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
       </c>
       <c r="I68" t="n">
         <v>1</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Frank Brandt</t>
+          <t>Robin Diaz, Miriam Avello</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>R15</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ANF,-:X,- (N75)</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>UL:W; LL:R; UR:Y; LR:B</t>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>3 banded PIPL</t>
+          <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5058,59 +5066,59 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>clear, 48F, Nwind @ 20kn</t>
+          <t>light rain first 90 min; cloudy; &lt;5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>North Anclote Bar</t>
+          <t>Crandon Park Beach, Key Biscayne</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>28.23463</v>
+        <v>25.701205</v>
       </c>
       <c r="G69" t="n">
-        <v>-82.8372</v>
-      </c>
-      <c r="H69" t="n">
-        <v>2</v>
+        <v>-80.154668</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
       </c>
       <c r="I69" t="n">
         <v>1</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Frank Brandt</t>
-        </is>
-      </c>
-      <c r="K69" t="n">
-        <v>556</v>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Robin Diaz, Miriam Avello</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X,O/Y:O,Y</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>UL:B; LL:Y; UR:Y; LR:R</t>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>3 banded PIPL</t>
+          <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5132,57 +5140,51 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>clear, 48F, Nwind @ 20kn</t>
+          <t>light rain first 90 min; cloudy; &lt;5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>North Anclote Bar</t>
+          <t>Crandon Park Beach, Key Biscayne</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>28.23463</v>
+        <v>25.701205</v>
       </c>
       <c r="G70" t="n">
-        <v>-82.8372</v>
-      </c>
-      <c r="H70" t="n">
+        <v>-80.154668</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
         <v>2</v>
       </c>
-      <c r="I70" t="n">
-        <v>1</v>
-      </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Frank Brandt</t>
+          <t>Robin Diaz, Miriam Avello</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Lb</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>UL:W; LL:W; UR:W; LR:R</t>
-        </is>
-      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>3 banded PIPL</t>
+          <t>3 PIPL banded (see Data Sheet 3)</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5204,49 +5206,59 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>clear, 48F, Nwind @ 20kn</t>
+          <t>light rain first 90 min; cloudy; &lt;5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>North Anclote Bar</t>
+          <t>Crandon Park Beach, Key Biscayne</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>28.23463</v>
+        <v>25.700689</v>
       </c>
       <c r="G71" t="n">
-        <v>-82.8372</v>
-      </c>
-      <c r="H71" t="n">
-        <v>2</v>
+        <v>-80.154995</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
       </c>
       <c r="I71" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Frank Brandt</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>Robin Diaz, Miriam Avello</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X,YG:bf,GK</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>3 banded PIPL</t>
+          <t>2 PIPL banded (see Data Sheet 3) | Band: photo available</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5268,47 +5280,61 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>wind 15 mph, 50-60F, sunny</t>
+          <t>light rain first 90 min; cloudy; &lt;5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Three Rooker Island - North &amp; Middle</t>
+          <t>Crandon Park Beach, Key Biscayne</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>28.1309</v>
+        <v>25.700689</v>
       </c>
       <c r="G72" t="n">
-        <v>-82.82928</v>
-      </c>
-      <c r="H72" t="n">
-        <v>2</v>
+        <v>-80.154995</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
       </c>
       <c r="I72" t="n">
         <v>1</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>Robin Diaz, Miriam Avello</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O(green dot),-:X,Y</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>2 PIPL banded (see Data Sheet 3) | Band: photo available</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -5328,47 +5354,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>wind 15 mph, 50-60F, sunny</t>
+          <t>light rain first 90 min; cloudy; &lt;5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Three Rooker Island - North &amp; Middle</t>
+          <t>Crandon Park Beach, Key Biscayne</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>28.13042</v>
+        <v>25.700689</v>
       </c>
       <c r="G73" t="n">
-        <v>-82.83038000000001</v>
-      </c>
-      <c r="H73" t="n">
-        <v>3</v>
+        <v>-80.154995</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
+          <t>Robin Diaz, Miriam Avello</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2 PIPL banded (see Data Sheet 3)</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -5388,61 +5420,59 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>wind 15 mph, 50-60F, sunny</t>
+          <t>light rain first 90 min; cloudy; &lt;5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Three Rooker Island - North &amp; Middle</t>
+          <t>Crandon Park Beach, Key Biscayne</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>28.12978</v>
+        <v>25.70208</v>
       </c>
       <c r="G74" t="n">
-        <v>-82.83185</v>
-      </c>
-      <c r="H74" t="n">
-        <v>4</v>
+        <v>-80.15433400000001</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
       </c>
       <c r="I74" t="n">
         <v>1</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
+          <t>Robin Diaz, Miriam Avello</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>ANF(CC2),-:O(840),-</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>UL:S; LL:Lb or Lg; LR:0</t>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Band: 2nd observer thought lower left band color was Lg.</t>
+          <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5464,47 +5494,61 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>wind 15 mph, 50-60F, sunny</t>
+          <t>light rain first 90 min; cloudy; &lt;5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Three Rooker Island - North &amp; Middle</t>
+          <t>Crandon Park Beach, Key Biscayne</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>28.12978</v>
+        <v>25.70208</v>
       </c>
       <c r="G75" t="n">
-        <v>-82.83185</v>
-      </c>
-      <c r="H75" t="n">
-        <v>4</v>
+        <v>-80.15433400000001</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
       </c>
       <c r="I75" t="n">
         <v>1</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>Robin Diaz, Miriam Avello</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X,bR:ANF,YG (T74)</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -5524,47 +5568,61 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>wind 15 mph, 50-60F, sunny</t>
+          <t>light rain first 90 min; cloudy; &lt;5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Three Rooker Island - North &amp; Middle</t>
+          <t>Crandon Park Beach, Key Biscayne</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>28.12857</v>
+        <v>25.70208</v>
       </c>
       <c r="G76" t="n">
-        <v>-82.83378</v>
-      </c>
-      <c r="H76" t="n">
-        <v>5</v>
+        <v>-80.15433400000001</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
       </c>
       <c r="I76" t="n">
         <v>1</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>Robin Diaz, Miriam Avello</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Of,GG:X,Y</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -5584,49 +5642,59 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>wind 15 mph, 50-60F, sunny</t>
+          <t>light rain first 90 min; cloudy; &lt;5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Three Rooker Island - North &amp; Middle</t>
+          <t>Crandon Park Beach, Key Biscayne</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>28.12717</v>
+        <v>25.70208</v>
       </c>
       <c r="G77" t="n">
-        <v>-82.83511</v>
-      </c>
-      <c r="H77" t="n">
-        <v>6</v>
+        <v>-80.15433400000001</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
       </c>
       <c r="I77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>Robin Diaz, Miriam Avello</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Of,OR:X,Y</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>1 SNPL adult male, the other two:sex indeterminate</t>
+          <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -5648,41 +5716,43 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>wind 15 mph, 50-60F, sunny</t>
+          <t>light rain first 90 min; cloudy; &lt;5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Three Rooker Island - North &amp; Middle</t>
+          <t>Crandon Park Beach, Key Biscayne</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>28.1259</v>
+        <v>25.70208</v>
       </c>
       <c r="G78" t="n">
-        <v>-82.83642</v>
-      </c>
-      <c r="H78" t="n">
+        <v>-80.15433400000001</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
         <v>7</v>
       </c>
-      <c r="I78" t="n">
-        <v>2</v>
-      </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
+          <t>Robin Diaz, Miriam Avello</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5690,7 +5760,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>SNPL had no toes on left leg</t>
+          <t>4 PIPL banded (see Data Sheet 3)</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -5712,47 +5782,59 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>42041</v>
+        <v>42046</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>08:45 - 10:45</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>wind 15 mph, 50-60F, sunny</t>
+          <t>63 F, 9.7 E. winds, partly cloudy</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Three Rooker Island - North &amp; Middle</t>
+          <t>Boca Grande Key</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>28.12521</v>
+        <v>24.53105</v>
       </c>
       <c r="G79" t="n">
-        <v>-82.83672</v>
+        <v>-82.00763999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
+          <t>Patty Kelly, Sid Maddock, F. Bell</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Flg Lb</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>UL:FWS; LL:Y/R; UR:Flg Lb; LR:K/K</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>foraging nearby mixed flock on interior mud and algal flats.</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -5772,61 +5854,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>42041</v>
+        <v>42046</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>08:45 - 10:45</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>wind 15 mph, 50-60F, sunny</t>
+          <t>63 F, 9.7 E. winds, partly cloudy</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Three Rooker Island - North &amp; Middle</t>
+          <t>Boca Grande Key</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>28.11836</v>
+        <v>24.53105</v>
       </c>
       <c r="G80" t="n">
-        <v>-82.83859</v>
+        <v>-82.00763999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>UL:F(G); LL:B/B; LR:Y/W</t>
-        </is>
-      </c>
+          <t>Patty Kelly, Sid Maddock, F. Bell</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>3 pairs of AMOY visible on this section of beach at all times</t>
+          <t>foraging nearby mixed flock on interior mud and algal flats.</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -5848,61 +5918,61 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B81" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>wind 15 mph, 50-60F, sunny</t>
+          <t>clear, 48F, Nwind @ 20kn</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Three Rooker Island - North &amp; Middle</t>
+          <t>North Anclote Bar</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>28.11738</v>
+        <v>28.23463</v>
       </c>
       <c r="G81" t="n">
-        <v>-82.83866999999999</v>
+        <v>-82.8372</v>
       </c>
       <c r="H81" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
+          <t>Frank Brandt</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>UL:F(G); LL:K; UR:G</t>
+          <t>UL:W; LL:R; UR:Y; LR:B</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>3 pairs of AMOY visible on this section of beach at all times</t>
+          <t>3 banded PIPL</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -5924,49 +5994,59 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="B82" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>wind 15 mph, 50-60F, sunny</t>
+          <t>clear, 48F, Nwind @ 20kn</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Three Rooker Island - North &amp; Middle</t>
+          <t>North Anclote Bar</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>28.11574</v>
+        <v>28.23463</v>
       </c>
       <c r="G82" t="n">
-        <v>-82.83868</v>
+        <v>-82.8372</v>
       </c>
       <c r="H82" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I82" t="n">
         <v>1</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
+          <t>Frank Brandt</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>556</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>UL:B; LL:Y; UR:Y; LR:R</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>3 pairs of AMOY visible on this section of beach at all times</t>
+          <t>3 banded PIPL</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -5988,59 +6068,59 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B83" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>wind 15 mph, 50-60F, sunny</t>
+          <t>clear, 48F, Nwind @ 20kn</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Three Rooker Island - North &amp; Middle</t>
+          <t>North Anclote Bar</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>28.11453</v>
+        <v>28.23463</v>
       </c>
       <c r="G83" t="n">
-        <v>-82.83853000000001</v>
+        <v>-82.8372</v>
       </c>
       <c r="H83" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
+          <t>Frank Brandt</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Lb</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Orientation:horizontal; UL:S; UR:F(A)</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>UL:W; LL:W; UR:W; LR:R</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>3 banded PIPL</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -6060,47 +6140,51 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B84" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>wind 15 mph, 50-60F, sunny</t>
+          <t>clear, 48F, Nwind @ 20kn</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Three Rooker Island - North &amp; Middle</t>
+          <t>North Anclote Bar</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>28.11453</v>
+        <v>28.23463</v>
       </c>
       <c r="G84" t="n">
-        <v>-82.83853000000001</v>
+        <v>-82.8372</v>
       </c>
       <c r="H84" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
+          <t>Frank Brandt</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>3 banded PIPL</t>
+        </is>
+      </c>
       <c r="O84" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -6120,51 +6204,47 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B85" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>09:12-10:35</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>clear, 48F, Nwind @ 20kn</t>
+          <t>wind 15 mph, 50-60F, sunny</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Honeymoon Island, North route</t>
+          <t>Three Rooker Island - North &amp; Middle</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>28.094143</v>
+        <v>28.1309</v>
       </c>
       <c r="G85" t="n">
-        <v>-82.83369999999999</v>
+        <v>-82.82928</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Wilf Yusek, Brooke Hoerner</t>
+          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no bands </t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -6184,63 +6264,47 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B86" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>clear, 48F, Nwind @ 20kn</t>
+          <t>wind 15 mph, 50-60F, sunny</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Anclote Key, South route</t>
+          <t>Three Rooker Island - North &amp; Middle</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>28.16277</v>
+        <v>28.13042</v>
       </c>
       <c r="G86" t="n">
-        <v>-82.84496</v>
+        <v>-82.83038000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Dan Larremore</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>A19</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>UL:F(Y); LL:B/Y; UR:S; LR:Y/K</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>1 banded SNPL, 5 banded PIPL</t>
-        </is>
-      </c>
+          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -6260,61 +6324,61 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B87" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>clear, 48F, Nwind @ 20kn</t>
+          <t>wind 15 mph, 50-60F, sunny</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Anclote Key, South route</t>
+          <t>Three Rooker Island - North &amp; Middle</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>28.16277</v>
+        <v>28.12978</v>
       </c>
       <c r="G87" t="n">
-        <v>-82.84496</v>
+        <v>-82.83185</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Dan Larremore</t>
+          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>EMI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>UL:F(W); UR:S</t>
+          <t>UL:S; LL:Lb or Lg; UR:-; LR:0</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>1 banded SNPL, 5 banded PIPL | Band: Not 100% on digits</t>
+          <t>Band: 2nd observer thought lower left band color was Lg.</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -6336,63 +6400,47 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B88" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>clear, 48F, Nwind @ 20kn</t>
+          <t>wind 15 mph, 50-60F, sunny</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Anclote Key, South route</t>
+          <t>Three Rooker Island - North &amp; Middle</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>28.16277</v>
+        <v>28.12978</v>
       </c>
       <c r="G88" t="n">
-        <v>-82.84496</v>
+        <v>-82.83185</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Dan Larremore</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>UL:F(G); LL:W/O; UR:Y</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>1 banded SNPL, 5 banded PIPL</t>
-        </is>
-      </c>
+          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -6412,51 +6460,47 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="B89" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>clear, 48F, Nwind @ 20kn</t>
+          <t>wind 15 mph, 50-60F, sunny</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Anclote Key, South route</t>
+          <t>Three Rooker Island - North &amp; Middle</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>28.16277</v>
+        <v>28.12857</v>
       </c>
       <c r="G89" t="n">
-        <v>-82.84496</v>
+        <v>-82.83378</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I89" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Dan Larremore</t>
+          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>1 banded SNPL, 5 banded PIPL</t>
-        </is>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -6476,41 +6520,41 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B90" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>clear, 48F, Nwind @ 20kn</t>
+          <t>wind 15 mph, 50-60F, sunny</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Anclote Key, South route</t>
+          <t>Three Rooker Island - North &amp; Middle</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>28.1597</v>
+        <v>28.12717</v>
       </c>
       <c r="G90" t="n">
-        <v>-82.84018</v>
+        <v>-82.83511</v>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Dan Larremore</t>
+          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -6518,7 +6562,7 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>1 banded SNPL</t>
+          <t>1 SNPL adult male, the other two:sex indeterminate</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6540,37 +6584,41 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>42042</v>
+        <v>42041</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>10:30 AM-12:30 PM</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Clear, sunny 60F light wind</t>
+          <t>wind 15 mph, 50-60F, sunny</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Outback Key</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+          <t>Three Rooker Island - North &amp; Middle</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>28.1259</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-82.83642</v>
+      </c>
       <c r="H91" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I91" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Lorraine and Don Margeson</t>
+          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6578,7 +6626,7 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>banded SNPL, PIPL and WIPL</t>
+          <t>SNPL had no toes on left leg</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -6600,59 +6648,47 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B92" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Wind 10-15 mph, clear, sunny.</t>
+          <t>wind 15 mph, 50-60F, sunny</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Three Rooker Bar South</t>
+          <t>Three Rooker Island - North &amp; Middle</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>28.11158</v>
+        <v>28.12521</v>
       </c>
       <c r="G92" t="n">
-        <v>-82.83702</v>
+        <v>-82.83672</v>
       </c>
       <c r="H92" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Stephen Mann, Robert Lane</t>
+          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>FO</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>UL:FO; LL:Y; UR:S; LR:K</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>2 banded PIPL | Band: With big group of PIPLs</t>
-        </is>
-      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -6672,49 +6708,61 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B93" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wind 10-15 mph, clear, sunny.</t>
+          <t>wind 15 mph, 50-60F, sunny</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Three Rooker Bar South</t>
+          <t>Three Rooker Island - North &amp; Middle</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>28.11158</v>
+        <v>28.11836</v>
       </c>
       <c r="G93" t="n">
-        <v>-82.83702</v>
+        <v>-82.83859</v>
       </c>
       <c r="H93" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I93" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Stephen Mann, Robert Lane</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
+          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>UL:F(G); LL:B/B; UR:-; LR:Y/W</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2 banded PIPL</t>
+          <t>3 pairs of AMOY visible on this section of beach at all times</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -6736,49 +6784,61 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B94" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wind 10-15 mph, clear, sunny.</t>
+          <t>wind 15 mph, 50-60F, sunny</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Three Rooker Bar South</t>
+          <t>Three Rooker Island - North &amp; Middle</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>28.10613</v>
+        <v>28.11738</v>
       </c>
       <c r="G94" t="n">
-        <v>-82.83335</v>
+        <v>-82.83866999999999</v>
       </c>
       <c r="H94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Stephen Mann, Robert Lane</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
+          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>UL:F(G); LL:K; UR:G; LR:-</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Red Knots may have been seen earlier on intercoastal side. Just about same number.</t>
+          <t>3 pairs of AMOY visible on this section of beach at all times</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -6800,41 +6860,41 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B95" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Wind 10-15 mph, clear, sunny.</t>
+          <t>wind 15 mph, 50-60F, sunny</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Three Rooker Bar South</t>
+          <t>Three Rooker Island - North &amp; Middle</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>28.10598</v>
+        <v>28.11574</v>
       </c>
       <c r="G95" t="n">
-        <v>-82.83507</v>
+        <v>-82.83868</v>
       </c>
       <c r="H95" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I95" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Stephen Mann, Robert Lane</t>
+          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6842,7 +6902,7 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Second group of Red Knots, first group visible from this location.</t>
+          <t>3 pairs of AMOY visible on this section of beach at all times</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -6864,63 +6924,59 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B96" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>12:45 - 16:00</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Low tide rising, 10% cloud cover, no precipitation, calm surf, winds 4-7mph</t>
+          <t>wind 15 mph, 50-60F, sunny</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Big Sabine</t>
+          <t>Three Rooker Island - North &amp; Middle</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>30.35707</v>
+        <v>28.11453</v>
       </c>
       <c r="G96" t="n">
-        <v>-87.04765</v>
+        <v>-82.83853000000001</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Kevin Christman</t>
+          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1B0</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:FY; UR:S</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>Bay Flat, 13:55, all feeding, sparse wrack, 4 banded PIPL | Band: Photos taken. FY//:S//</t>
-        </is>
-      </c>
+          <t>Orientation:horizontal; UL:S; LL:-; UR:F(A); LR:-</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -6940,63 +6996,47 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="B97" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>12:45 - 16:00</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Low tide rising, 10% cloud cover, no precipitation, calm surf, winds 4-7mph</t>
+          <t>wind 15 mph, 50-60F, sunny</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Big Sabine</t>
+          <t>Three Rooker Island - North &amp; Middle</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>30.35707</v>
+        <v>28.11453</v>
       </c>
       <c r="G97" t="n">
-        <v>-87.04765</v>
+        <v>-82.83853000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I97" t="n">
         <v>1</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Kevin Christman</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>E91</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Orientation:Horizontal; UL:S; LL:YK; UR:FY; LR:GB</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>Bay Flat, 13:55, all feeding, sparse wrack, 4 banded PIPL | Band: Photos taken. S//YK:FY//GB</t>
-        </is>
-      </c>
+          <t>Marianne Korosy, Dana Kerstein, Barbara Bleakley</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -7016,57 +7056,49 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B98" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>12:45 - 16:00</t>
+          <t>09:12 - 10:35</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Low tide rising, 10% cloud cover, no precipitation, calm surf, winds 4-7mph</t>
+          <t>clear, 48F, Nwind @ 20kn</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Big Sabine</t>
+          <t>Honeymoon Island, North route</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>30.35707</v>
+        <v>28.094143</v>
       </c>
       <c r="G98" t="n">
-        <v>-87.04765</v>
+        <v>-82.83369999999999</v>
       </c>
       <c r="H98" t="n">
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Kevin Christman</t>
+          <t>Wilf Yusek, Brooke Hoerner</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>UL:FG; LL:BG; LR:WB</t>
-        </is>
-      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Bay Flat, 13:55, all feeding, sparse wrack, 4 banded PIPL | Band: Photo taken. FG//BG:WB</t>
+          <t xml:space="preserve">no bands </t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7088,31 +7120,31 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="B99" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>12:45 - 16:00</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Low tide rising, 10% cloud cover, no precipitation, calm surf, winds 4-7mph</t>
+          <t>clear, 48F, Nwind @ 20kn</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Big Sabine</t>
+          <t>Anclote Key, South route</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>30.35707</v>
+        <v>28.16277</v>
       </c>
       <c r="G99" t="n">
-        <v>-87.04765</v>
+        <v>-82.84496</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
@@ -7122,27 +7154,27 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Kevin Christman</t>
+          <t>Dan Larremore</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:FY; LL:GB; LR:GP</t>
+          <t>UL:F(Y); LL:B/Y; UR:S; LR:Y/K</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Bay Flat, 13:55, all feeding, sparse wrack, 4 banded PIPL | Band: Photo taken. Faded pink. FY//GB:GP</t>
+          <t>1 banded SNPL, 5 banded PIPL</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -7164,49 +7196,61 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B100" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>12:45 - 16:00</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Low tide rising, 10% cloud cover, no precipitation, calm surf, winds 4-7mph</t>
+          <t>clear, 48F, Nwind @ 20kn</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Big Sabine</t>
+          <t>Anclote Key, South route</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>30.35707</v>
+        <v>28.16277</v>
       </c>
       <c r="G100" t="n">
-        <v>-87.04765</v>
+        <v>-82.84496</v>
       </c>
       <c r="H100" t="n">
         <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Kevin Christman</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
+          <t>Dan Larremore</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>EMI</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>UL:F(W); LL:-; UR:S; LR:-</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Bay Flat, 13:55, all feeding, sparse wrack, 4 banded PIPL</t>
+          <t>1 banded SNPL, 5 banded PIPL | Band: Not 100% on digits</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -7228,49 +7272,61 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B101" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>12:45 - 16:00</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Low tide rising, 10% cloud cover, no precipitation, calm surf, winds 4-7mph</t>
+          <t>clear, 48F, Nwind @ 20kn</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Big Sabine</t>
+          <t>Anclote Key, South route</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>30.35743</v>
+        <v>28.16277</v>
       </c>
       <c r="G101" t="n">
-        <v>-87.04361</v>
+        <v>-82.84496</v>
       </c>
       <c r="H101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Kevin Christman</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
+          <t>Dan Larremore</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>UL:F(G); LL:W/O; UR:Y; LR:-</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Inlet Spit, 14:25, feeding and resting, sparse wrack, 0 banded PIPL, 15 banded SNPL - only 8 confirmed, other combos were incomplete readings.</t>
+          <t>1 banded SNPL, 5 banded PIPL</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7292,57 +7348,61 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B102" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>16:51 - 17:45</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mid tide rising, 20% cloud cover, no precipitation, calm surf, winds 0-3mph</t>
+          <t>clear, 48F, Nwind @ 20kn</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Navarre</t>
+          <t>Anclote Key, South route</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>30.38595</v>
+        <v>28.16277</v>
       </c>
       <c r="G102" t="n">
-        <v>-86.8685357</v>
+        <v>-82.84496</v>
       </c>
       <c r="H102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Kevin Christman</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
+          <t>Dan Larremore</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>G</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>UL:S; LL:W; UR:FY; LR:K</t>
+          <t>UL:-; LL:W/W; UR:F(G); LR:O/Y</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>1 banded PIPL, Lake/Creek Outfall, 17:31, no wrack, all feeding | Band: No code, missing band. S//W:FY//K - photo taken</t>
+          <t>1 banded SNPL, 5 banded PIPL</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -7364,49 +7424,61 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="B103" s="1" t="n">
-        <v>42045</v>
+        <v>42041</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>12:25 - 15:15</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>cloudy, windy, cool</t>
+          <t>clear, 48F, Nwind @ 20kn</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ponce Inlet Parks and Disappearing Island</t>
+          <t>Anclote Key, South route</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>29.06883</v>
+        <v>28.16277</v>
       </c>
       <c r="G103" t="n">
-        <v>-80.92652699999999</v>
+        <v>-82.84496</v>
       </c>
       <c r="H103" t="n">
         <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Jennifer Winters, Stacey Bell, Michael Brothers, Amber Stevenson</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
+          <t>Dan Larremore</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>UL:S; LL:K/G; UR:F(G); LR:G/B</t>
+        </is>
+      </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>none banded</t>
+          <t>1 banded SNPL, 5 banded PIPL</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -7428,41 +7500,41 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B104" s="1" t="n">
-        <v>42045</v>
+        <v>42041</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>12:25 - 15:15</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>cloudy, windy, cool</t>
+          <t>clear, 48F, Nwind @ 20kn</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ponce Inlet Parks and Disappearing Island</t>
+          <t>Anclote Key, South route</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>29.069134</v>
+        <v>28.16277</v>
       </c>
       <c r="G104" t="n">
-        <v>-80.925488</v>
+        <v>-82.84496</v>
       </c>
       <c r="H104" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Jennifer Winters, Stacey Bell, Michael Brothers, Amber Stevenson</t>
+          <t>Dan Larremore</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -7470,7 +7542,7 @@
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>none banded</t>
+          <t>1 banded SNPL, 5 banded PIPL</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -7492,53 +7564,49 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>42045</v>
+        <v>42041</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>12:25 - 15:15</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>cloudy, windy, cool</t>
+          <t>clear, 48F, Nwind @ 20kn</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ponce Inlet Parks and Disappearing Island</t>
+          <t>Anclote Key, South route</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>29.069885</v>
+        <v>28.1597</v>
       </c>
       <c r="G105" t="n">
-        <v>-80.925816</v>
+        <v>-82.84018</v>
       </c>
       <c r="H105" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Jennifer Winters, Stacey Bell, Michael Brothers, Amber Stevenson</t>
+          <t>Dan Larremore</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>UL:S; LL:KOK; UR:O; LR:K</t>
-        </is>
-      </c>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2 banded PIPL | Band: Black/Orange/Black split band on Lower Left; Orange band on Upper Right has green circular dot, Black band on Lower Right has white lettering (not confirmed, but previously observed 94), photos available</t>
+          <t>1 banded SNPL</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -7560,41 +7628,37 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>42045</v>
+        <v>42042</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>12:25 - 15:15</t>
+          <t>10:30 - 12:30</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>cloudy, windy, cool</t>
+          <t>Clear, sunny 60F light wind</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ponce Inlet Parks and Disappearing Island</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>29.070111</v>
-      </c>
-      <c r="G106" t="n">
-        <v>-80.926294</v>
-      </c>
+          <t>Outback Key</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Jennifer Winters, Stacey Bell, Michael Brothers, Amber Stevenson</t>
+          <t>Lorraine and Don Margeson</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -7602,7 +7666,7 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>none banded</t>
+          <t>banded SNPL, PIPL and WIPL</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -7624,41 +7688,41 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B107" s="1" t="n">
-        <v>42045</v>
+        <v>42041</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>12:25 - 15:15</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>cloudy, windy, cool</t>
+          <t>Wind 10-15 mph, clear, sunny.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ponce Inlet Parks and Disappearing Island</t>
+          <t>Three Rooker Bar South</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>29.072017</v>
+        <v>28.11158</v>
       </c>
       <c r="G107" t="n">
-        <v>-80.928044</v>
+        <v>-82.83702</v>
       </c>
       <c r="H107" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I107" t="n">
         <v>1</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Jennifer Winters, Stacey Bell, Michael Brothers, Amber Stevenson</t>
+          <t>Stephen Mann, Robert Lane</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -7669,12 +7733,12 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>UL:FO; LL:KO/Y; UR:S; LR:Lb</t>
+          <t>UL:FO; LL:Y; UR:S; LR:K</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>1 banded PIPL | Band: Black/Orange split band over Yellow on Lower Left, photos available</t>
+          <t>2 banded PIPL | Band: With big group of PIPLs</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -7696,49 +7760,57 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B108" s="1" t="n">
-        <v>42045</v>
+        <v>42041</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>12:25 - 15:15</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>cloudy, windy, cool</t>
+          <t>Wind 10-15 mph, clear, sunny.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ponce Inlet Parks and Disappearing Island</t>
+          <t>Three Rooker Bar South</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>29.072017</v>
+        <v>28.11158</v>
       </c>
       <c r="G108" t="n">
-        <v>-80.928044</v>
+        <v>-82.83702</v>
       </c>
       <c r="H108" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Jennifer Winters, Stacey Bell, Michael Brothers, Amber Stevenson</t>
+          <t>Stephen Mann, Robert Lane</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>UL:FB; LL:G/R; UR:S; LR:K</t>
+        </is>
+      </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>1 banded PIPL</t>
+          <t>2 banded PIPL | Band: With big group of PIPLs</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -7760,41 +7832,41 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B109" s="1" t="n">
-        <v>42045</v>
+        <v>42041</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>07:45 / 17:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>57/62 degrees, NW wind 10-15 knots 85% cloud cover</t>
+          <t>Wind 10-15 mph, clear, sunny.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Volusia Atlantic Shore, North</t>
+          <t>Three Rooker Bar South</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>29.081667</v>
+        <v>28.11158</v>
       </c>
       <c r="G109" t="n">
-        <v>-80.921389</v>
+        <v>-82.83702</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>David Hartgrove</t>
+          <t>Stephen Mann, Robert Lane</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7802,7 +7874,7 @@
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>No Bands</t>
+          <t>2 banded PIPL</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -7820,55 +7892,55 @@
           <t>DATA SHEET 1</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>Longitude sign corrected: 80.921389 → -80.921389</t>
-        </is>
-      </c>
+      <c r="R109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B110" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>11:44-1:21</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">sunny, 52 degrees, wind E 5 mph, tide extremely low </t>
+          <t>Wind 10-15 mph, clear, sunny.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Big Sabine Bay</t>
+          <t>Three Rooker Bar South</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>30.355967</v>
+        <v>28.10613</v>
       </c>
       <c r="G110" t="n">
-        <v>-87.043892</v>
+        <v>-82.83335</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Rob Holbrook; Emile Lores</t>
+          <t>Stephen Mann, Robert Lane</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Red Knots may have been seen earlier on intercoastal side. Just about same number.</t>
+        </is>
+      </c>
       <c r="O110" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -7888,47 +7960,51 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B111" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>11:44-1:21</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">sunny, 52 degrees, wind E 5 mph, tide extremely low </t>
+          <t>Wind 10-15 mph, clear, sunny.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Big Sabine Bay</t>
+          <t>Three Rooker Bar South</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>30.356508</v>
+        <v>28.10598</v>
       </c>
       <c r="G111" t="n">
-        <v>-87.043953</v>
+        <v>-82.83507</v>
       </c>
       <c r="H111" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Rob Holbrook; Emile Lores</t>
+          <t>Stephen Mann, Robert Lane</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Second group of Red Knots, first group visible from this location.</t>
+        </is>
+      </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>WinterBirdSurvey</t>
@@ -7945,6 +8021,1222 @@
         </is>
       </c>
       <c r="R111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>42041</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>12:45 - 16:00</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Low tide rising, 10% cloud cover, no precipitation, calm surf, winds 4-7mph</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Big Sabine</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>30.35707</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-87.04765</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Kevin Christman</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>1B0</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Orientation:Horizontal; UL:FY; LL:-; UR:S; LR:-</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Bay Flat, 13:55, all feeding, sparse wrack, 4 banded PIPL | Band: Photos taken. FY//:S//</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>42041</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>12:45 - 16:00</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Low tide rising, 10% cloud cover, no precipitation, calm surf, winds 4-7mph</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Big Sabine</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>30.35707</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-87.04765</v>
+      </c>
+      <c r="H113" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Kevin Christman</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>E91</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Orientation:Horizontal; UL:S; LL:YK; UR:FY; LR:GB</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Bay Flat, 13:55, all feeding, sparse wrack, 4 banded PIPL | Band: Photos taken. S//YK:FY//GB</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>42041</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>12:45 - 16:00</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Low tide rising, 10% cloud cover, no precipitation, calm surf, winds 4-7mph</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Big Sabine</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>30.35707</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-87.04765</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Kevin Christman</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>UL:FG; LL:BG; UR:-; LR:WB</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Bay Flat, 13:55, all feeding, sparse wrack, 4 banded PIPL | Band: Photo taken. FG//BG:WB</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="1" t="n">
+        <v>42041</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>12:45 - 16:00</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Low tide rising, 10% cloud cover, no precipitation, calm surf, winds 4-7mph</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Big Sabine</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>30.35707</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-87.04765</v>
+      </c>
+      <c r="H115" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Kevin Christman</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Orientation:Horizontal; UL:FY; LL:GB; UR:-; LR:GP</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Bay Flat, 13:55, all feeding, sparse wrack, 4 banded PIPL | Band: Photo taken. Faded pink. FY//GB:GP</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>42041</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>12:45 - 16:00</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Low tide rising, 10% cloud cover, no precipitation, calm surf, winds 4-7mph</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Big Sabine</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>30.35707</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-87.04765</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="n">
+        <v>9</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Kevin Christman</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Bay Flat, 13:55, all feeding, sparse wrack, 4 banded PIPL</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="1" t="n">
+        <v>42041</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>12:45 - 16:00</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Low tide rising, 10% cloud cover, no precipitation, calm surf, winds 4-7mph</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Big Sabine</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>30.35743</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-87.04361</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2</v>
+      </c>
+      <c r="I117" t="n">
+        <v>2</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Kevin Christman</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Inlet Spit, 14:25, feeding and resting, sparse wrack, 0 banded PIPL, 15 banded SNPL - only 8 confirmed, other combos were incomplete readings.</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="1" t="n">
+        <v>42041</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>16:51 - 17:45</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Mid tide rising, 20% cloud cover, no precipitation, calm surf, winds 0-3mph</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Navarre</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>30.38595</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-86.8685357</v>
+      </c>
+      <c r="H118" t="n">
+        <v>3</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Kevin Christman</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>UL:S; LL:W; UR:FY; LR:K</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>1 banded PIPL, Lake/Creek Outfall, 17:31, no wrack, all feeding | Band: No code, missing band. S//W:FY//K - photo taken</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="1" t="n">
+        <v>42041</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>16:51 - 17:45</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Mid tide rising, 20% cloud cover, no precipitation, calm surf, winds 0-3mph</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Navarre</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>30.38595</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-86.8685357</v>
+      </c>
+      <c r="H119" t="n">
+        <v>3</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Kevin Christman</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>1 banded PIPL, Lake/Creek Outfall, 17:31, no wrack, all feeding</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="1" t="n">
+        <v>42045</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>12:25 - 15:15</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>cloudy, windy, cool</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Ponce Inlet Parks and Disappearing Island</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>29.06883</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-80.92652699999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="n">
+        <v>3</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Jennifer Winters, Stacey Bell, Michael Brothers, Amber Stevenson</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>none banded</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="1" t="n">
+        <v>42045</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>12:25 - 15:15</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>cloudy, windy, cool</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Ponce Inlet Parks and Disappearing Island</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>29.069134</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-80.925488</v>
+      </c>
+      <c r="H121" t="n">
+        <v>6</v>
+      </c>
+      <c r="I121" t="n">
+        <v>3</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Jennifer Winters, Stacey Bell, Michael Brothers, Amber Stevenson</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>none banded</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>42045</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>12:25 - 15:15</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>cloudy, windy, cool</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Ponce Inlet Parks and Disappearing Island</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>29.069885</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-80.925816</v>
+      </c>
+      <c r="H122" t="n">
+        <v>7</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Jennifer Winters, Stacey Bell, Michael Brothers, Amber Stevenson</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>UL:S; LL:KOK; UR:O; LR:K</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>2 banded PIPL | Band: Black/Orange/Black split band on Lower Left; Orange band on Upper Right has green circular dot, Black band on Lower Right has white lettering (not confirmed, but previously observed 94), photos available</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="1" t="n">
+        <v>42045</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>12:25 - 15:15</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>cloudy, windy, cool</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Ponce Inlet Parks and Disappearing Island</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>29.069885</v>
+      </c>
+      <c r="G123" t="n">
+        <v>-80.925816</v>
+      </c>
+      <c r="H123" t="n">
+        <v>7</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Jennifer Winters, Stacey Bell, Michael Brothers, Amber Stevenson</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>UL:S; LL:BO; UR:-; LR:-</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>2 banded PIPL | Band: photo blurry, confident ID</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="1" t="n">
+        <v>42045</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>12:25 - 15:15</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>cloudy, windy, cool</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Ponce Inlet Parks and Disappearing Island</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>29.070111</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-80.926294</v>
+      </c>
+      <c r="H124" t="n">
+        <v>8</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Jennifer Winters, Stacey Bell, Michael Brothers, Amber Stevenson</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>none banded</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="1" t="n">
+        <v>42045</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>12:25 - 15:15</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>cloudy, windy, cool</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Ponce Inlet Parks and Disappearing Island</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>29.072017</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-80.928044</v>
+      </c>
+      <c r="H125" t="n">
+        <v>9</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Jennifer Winters, Stacey Bell, Michael Brothers, Amber Stevenson</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>FO</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>UL:FO; LL:KO/Y; UR:S; LR:Lb</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>1 banded PIPL | Band: Black/Orange split band over Yellow on Lower Left, photos available</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="1" t="n">
+        <v>42045</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>12:25 - 15:15</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>cloudy, windy, cool</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Ponce Inlet Parks and Disappearing Island</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>29.072017</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-80.928044</v>
+      </c>
+      <c r="H126" t="n">
+        <v>9</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Jennifer Winters, Stacey Bell, Michael Brothers, Amber Stevenson</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>1 banded PIPL</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="1" t="n">
+        <v>42045</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>07:45 - 17:30</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>57/62 degrees, NW wind 10-15 knots 85% cloud cover</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Volusia Atlantic Shore, North</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>29.081667</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-80.921389</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>David Hartgrove</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>No Bands</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>Longitude sign corrected: 80.921389 → -80.921389</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="1" t="n">
+        <v>42041</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>11:44 - 01:21</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sunny, 52 degrees, wind E 5 mph, tide extremely low </t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Big Sabine Bay</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>30.355967</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-87.043892</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Rob Holbrook; Emile Lores</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="1" t="n">
+        <v>42041</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>11:44 - 01:21</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sunny, 52 degrees, wind E 5 mph, tide extremely low </t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Big Sabine Bay</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>30.356508</v>
+      </c>
+      <c r="G129" t="n">
+        <v>-87.043953</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2</v>
+      </c>
+      <c r="I129" t="n">
+        <v>2</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Rob Holbrook; Emile Lores</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>WinterBirdSurvey</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Winter Birds '15 Clean.xlsx</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>DATA SHEET 1</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
